--- a/fixed_trading_daily_bear.xlsx
+++ b/fixed_trading_daily_bear.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,6 +1515,924 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:29:47</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2588</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.5034</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.2588</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.3996</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:34:55</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.1904</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3896</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.1904</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.367</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:40:05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.3245</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.7625999999999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.3245</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.0672</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.445</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:45:12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.2809</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.5806</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2809</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.4398</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:50:19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.1278</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.1479</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.4869</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:55:32</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.352</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.6949</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.352</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1051</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.5304</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:00:43</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.357</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.7691</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.357</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.1121</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.5108</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:05:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.335</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.8307</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.335</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.08169999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.4777</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:11:03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.3751</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.7759</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.3751</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.137</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.5047</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:16:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.344</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.7153</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.344</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.0941</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.5174</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:21:03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.2058</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.5281</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.2058</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.342</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:26:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.2155</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.4882</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.2155</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.3691</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:31:13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1251</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.1777</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.1251</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.3313</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:36:06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.3078</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.6253</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.3078</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.4388</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:41:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.3706</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.7272</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.3706</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.1309</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.5373</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:45:53</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.4373</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.7899</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.4373</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.2229</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.5693</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:50:46</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.3358</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.6639</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.3358</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.0828</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.4916</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-09-10T22:55:38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.5034999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.9844000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.5034999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.3144</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.6526</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.0004947880017507564, "batch_size": 512, "gamma": 0.9743291355292365, "net_dimension": 512, "net_dims": [512, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixed_trading_daily_bear.xlsx
+++ b/fixed_trading_daily_bear.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2433,6 +2433,2046 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-09-11T07:53:38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.2476</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.6211</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.2476</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.3414</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-09-11T07:59:17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.3227</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.854</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.3227</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.4331</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:04:52</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.4477</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.7442</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.4477</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.2373</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.6318</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:10:38</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-1.0782</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:16:33</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.2147</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.4547</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.2147</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.4357</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:22:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.2653</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.6201</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.2653</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.4344</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:28:16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.0786</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.0786</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.335</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:34:02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.0745</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.0745</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.2888</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:39:40</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.2829</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.6726</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.2829</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.4055</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:45:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.4082</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.1101</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:50:59</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.2759</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.6274</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.2759</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.4666</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-09-11T08:56:42</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.2244</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.4281</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.2244</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.411</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:02:26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.3185</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.7879</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.3185</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.0589</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.4847</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:08:07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.2623</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.7151999999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.2623</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.3763</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:13:52</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.311</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.7038</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.311</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.4635</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:19:33</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.3334</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.8538</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.3334</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.0795</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.4031</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:25:13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.5046</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.365</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:30:52</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.1259</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.2606</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.1259</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.2836</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:36:25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>trial_018</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.2338</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.6457000000000001</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.2338</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.3825</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 330}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-09-11T09:42:04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>trial_019</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.3563</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.7868000000000001</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-0.3563</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.1111</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.5451</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 331}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:13:04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.2409</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.5478</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.2409</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.4103</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:17:49</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.2809</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.7329</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.2809</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.4475</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:22:31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.2735</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.6677999999999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.2735</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.4193</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:27:11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.4263</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.3474</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:31:52</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.2655</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.5954</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.2655</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.4087</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:36:41</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.3892</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.9193</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.3892</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-0.1565</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.5514</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:41:25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.5461</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.4823</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:46:12</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.2395</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-0.5382</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.2395</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.3924</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:50:58</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-0.8883</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.1678</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.534</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09-11T10:55:41</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-0.4906</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.5019</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:00:22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.2675</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-0.5748</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-0.2675</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.428</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:05:05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.2897</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-0.6142</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.2897</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.4553</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:09:46</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.1941</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.3362</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-0.1941</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.3517</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:14:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.2748</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-0.5996</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.2748</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.4235</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:19:07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.2735</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-0.5934</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.2735</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.4479</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:23:54</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.391</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0.391</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.159</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.5375</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:28:38</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.3041</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-0.6277</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.3041</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.0391</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.4505</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:33:17</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.2392</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-0.3885</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-0.2392</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-0.3997</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:38:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>trial_018</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.2022</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-0.5282</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-0.2022</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0.3486</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 330}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:42:45</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>trial_019</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.2609</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-0.6016</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.2609</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.4011</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 331}, "task": "trading", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
